--- a/data/trans_dic/P36B06_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,83; 83,63</t>
+          <t>77,67; 83,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,01; 89,03</t>
+          <t>83,96; 89,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,62; 83,95</t>
+          <t>77,4; 83,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,07; 88,36</t>
+          <t>83,3; 88,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,45; 91,89</t>
+          <t>87,42; 92,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,06; 84,8</t>
+          <t>78,71; 84,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,35; 85,09</t>
+          <t>81,27; 85,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>86,28; 89,84</t>
+          <t>86,32; 89,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,16; 83,48</t>
+          <t>79,2; 83,54</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,26; 76,48</t>
+          <t>70,09; 76,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,73; 84,62</t>
+          <t>79,77; 84,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,7; 81,7</t>
+          <t>76,63; 81,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,84; 80,98</t>
+          <t>75,7; 81,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,26; 89,67</t>
+          <t>85,47; 89,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,87; 83,3</t>
+          <t>77,8; 83,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,96; 77,8</t>
+          <t>73,86; 77,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,37; 86,62</t>
+          <t>83,43; 86,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78,3; 81,71</t>
+          <t>78,31; 81,84</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,2; 80,73</t>
+          <t>74,64; 80,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,83; 86,42</t>
+          <t>81,02; 86,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,69; 81,2</t>
+          <t>74,45; 80,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,75; 85,42</t>
+          <t>80,01; 85,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,06; 89,13</t>
+          <t>83,82; 88,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,77; 86,93</t>
+          <t>81,65; 86,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,91; 82,34</t>
+          <t>77,98; 82,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,01; 87,05</t>
+          <t>83,2; 87,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79,24; 83,23</t>
+          <t>79,08; 83,3</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,8; 77,19</t>
+          <t>71,77; 77,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,7; 84,77</t>
+          <t>79,36; 84,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,02; 84,24</t>
+          <t>79,33; 84,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,36; 83,26</t>
+          <t>78,42; 83,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,8; 89,02</t>
+          <t>85,16; 89,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,13; 88,41</t>
+          <t>84,04; 88,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,19; 79,83</t>
+          <t>76,0; 79,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,07; 86,38</t>
+          <t>83,1; 86,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82,61; 85,85</t>
+          <t>82,6; 85,82</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,82; 77,73</t>
+          <t>74,89; 77,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,2; 84,75</t>
+          <t>81,88; 84,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,54; 81,24</t>
+          <t>78,62; 81,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,24; 82,89</t>
+          <t>80,35; 82,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,71; 88,83</t>
+          <t>86,48; 88,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,12; 84,59</t>
+          <t>82,13; 84,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,85; 80,03</t>
+          <t>77,96; 80,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,79; 86,48</t>
+          <t>84,72; 86,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,71; 82,65</t>
+          <t>80,81; 82,67</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>539425; 579623</t>
+          <t>538299; 579121</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>590955; 626331</t>
+          <t>590611; 626729</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>522960; 565633</t>
+          <t>521485; 565009</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>571807; 608217</t>
+          <t>573425; 608145</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>609543; 640531</t>
+          <t>609377; 642379</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>531941; 570544</t>
+          <t>529580; 569503</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1123718; 1175397</t>
+          <t>1122685; 1177736</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1208423; 1258268</t>
+          <t>1208877; 1259009</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1065908; 1124085</t>
+          <t>1066529; 1124990</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>675023; 734811</t>
+          <t>673434; 731530</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>809257; 858914</t>
+          <t>809692; 860192</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>782001; 832985</t>
+          <t>781378; 835300</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>733580; 783382</t>
+          <t>732289; 785117</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>879072; 924552</t>
+          <t>881243; 925949</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>809177; 865679</t>
+          <t>808538; 863669</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1426008; 1500089</t>
+          <t>1424149; 1501618</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1705847; 1772354</t>
+          <t>1707148; 1771955</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1612051; 1682230</t>
+          <t>1612181; 1684969</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>503480; 547731</t>
+          <t>506417; 548803</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>610679; 652926</t>
+          <t>612132; 652374</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>566592; 615969</t>
+          <t>564751; 611773</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>545344; 584168</t>
+          <t>547141; 584919</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>651482; 690761</t>
+          <t>649609; 688966</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>641909; 682425</t>
+          <t>640933; 682453</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1061468; 1121705</t>
+          <t>1062352; 1121234</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1270490; 1332371</t>
+          <t>1273340; 1333280</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1223137; 1284661</t>
+          <t>1220640; 1285757</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>675910; 726604</t>
+          <t>675605; 728856</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>755391; 803438</t>
+          <t>752089; 799113</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>739327; 788132</t>
+          <t>742230; 790229</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>813062; 863955</t>
+          <t>813688; 863478</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>888519; 932763</t>
+          <t>892333; 935645</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>876389; 920968</t>
+          <t>875461; 918953</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1507757; 1579903</t>
+          <t>1504014; 1576334</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1657679; 1723772</t>
+          <t>1658390; 1719131</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1633459; 1697508</t>
+          <t>1633140; 1696960</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2449382; 2544630</t>
+          <t>2451498; 2550722</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2812667; 2899943</t>
+          <t>2801621; 2893006</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2660576; 2752130</t>
+          <t>2663191; 2759808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2709677; 2799375</t>
+          <t>2713392; 2798214</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3078892; 3154466</t>
+          <t>3070752; 3152914</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2905980; 2993329</t>
+          <t>2906414; 2999309</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5177785; 5322608</t>
+          <t>5185270; 5322071</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5912374; 6029929</t>
+          <t>5907117; 6026951</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5590496; 5724540</t>
+          <t>5597182; 5726172</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B06_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,67; 83,56</t>
+          <t>77,9; 83,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,96; 89,09</t>
+          <t>83,73; 88,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,4; 83,86</t>
+          <t>77,41; 83,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,3; 88,35</t>
+          <t>83,43; 88,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,42; 92,16</t>
+          <t>87,39; 92,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,71; 84,64</t>
+          <t>78,93; 84,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,27; 85,26</t>
+          <t>81,18; 85,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>86,32; 89,9</t>
+          <t>86,38; 89,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,2; 83,54</t>
+          <t>79,22; 83,41</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,09; 76,14</t>
+          <t>70,46; 76,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,77; 84,75</t>
+          <t>79,7; 84,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,63; 81,92</t>
+          <t>76,73; 81,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,7; 81,16</t>
+          <t>75,62; 81,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,47; 89,8</t>
+          <t>85,41; 89,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,8; 83,11</t>
+          <t>77,88; 82,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,86; 77,88</t>
+          <t>73,89; 78,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,43; 86,6</t>
+          <t>83,52; 86,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78,31; 81,84</t>
+          <t>78,14; 81,8</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,64; 80,88</t>
+          <t>74,06; 80,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,02; 86,35</t>
+          <t>80,57; 86,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,45; 80,65</t>
+          <t>74,12; 80,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,01; 85,53</t>
+          <t>79,82; 85,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,82; 88,9</t>
+          <t>83,64; 89,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,65; 86,94</t>
+          <t>81,56; 86,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,98; 82,3</t>
+          <t>78,23; 82,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,2; 87,11</t>
+          <t>83,16; 86,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79,08; 83,3</t>
+          <t>78,91; 83,08</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,77; 77,43</t>
+          <t>71,75; 77,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,36; 84,32</t>
+          <t>79,13; 84,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,33; 84,46</t>
+          <t>79,55; 84,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,42; 83,22</t>
+          <t>78,43; 83,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,16; 89,3</t>
+          <t>84,81; 89,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,04; 88,22</t>
+          <t>83,96; 88,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,0; 79,65</t>
+          <t>76,01; 79,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,1; 86,15</t>
+          <t>83,08; 86,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82,6; 85,82</t>
+          <t>82,61; 85,89</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,89; 77,92</t>
+          <t>74,74; 77,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,88; 84,55</t>
+          <t>82,04; 84,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,62; 81,47</t>
+          <t>78,63; 81,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,35; 82,86</t>
+          <t>80,33; 82,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,48; 88,79</t>
+          <t>86,68; 88,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,13; 84,76</t>
+          <t>82,03; 84,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,96; 80,02</t>
+          <t>78,01; 79,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,72; 86,44</t>
+          <t>84,73; 86,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,81; 82,67</t>
+          <t>80,73; 82,71</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>538299; 579121</t>
+          <t>539892; 580709</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>590611; 626729</t>
+          <t>589040; 625062</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>521485; 565009</t>
+          <t>521545; 564352</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>573425; 608145</t>
+          <t>574290; 607959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>609377; 642379</t>
+          <t>609162; 641335</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>529580; 569503</t>
+          <t>531042; 570174</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1122685; 1177736</t>
+          <t>1121440; 1176265</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1208877; 1259009</t>
+          <t>1209808; 1257386</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1066529; 1124990</t>
+          <t>1066738; 1123174</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>673434; 731530</t>
+          <t>676991; 732836</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>809692; 860192</t>
+          <t>808902; 860084</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>781378; 835300</t>
+          <t>782365; 832641</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>732289; 785117</t>
+          <t>731512; 784316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>881243; 925949</t>
+          <t>880633; 926718</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>808538; 863669</t>
+          <t>809350; 862226</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1424149; 1501618</t>
+          <t>1424576; 1504267</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1707148; 1771955</t>
+          <t>1708931; 1775805</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1612181; 1684969</t>
+          <t>1608753; 1684206</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>506417; 548803</t>
+          <t>502485; 547228</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>612132; 652374</t>
+          <t>608733; 652600</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>564751; 611773</t>
+          <t>562234; 612230</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>547141; 584919</t>
+          <t>545858; 585133</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>649609; 688966</t>
+          <t>648223; 689917</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>640933; 682453</t>
+          <t>640265; 682121</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1062352; 1121234</t>
+          <t>1065821; 1123840</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1273340; 1333280</t>
+          <t>1272777; 1331082</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1220640; 1285757</t>
+          <t>1218106; 1282462</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>675605; 728856</t>
+          <t>675444; 727313</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>752089; 799113</t>
+          <t>749956; 800813</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>742230; 790229</t>
+          <t>744258; 788593</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>813688; 863478</t>
+          <t>813859; 862247</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>892333; 935645</t>
+          <t>888685; 935123</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>875461; 918953</t>
+          <t>874562; 919323</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1504014; 1576334</t>
+          <t>1504257; 1577934</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1658390; 1719131</t>
+          <t>1657911; 1723431</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1633140; 1696960</t>
+          <t>1633410; 1698380</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2451498; 2550722</t>
+          <t>2446669; 2543041</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2801621; 2893006</t>
+          <t>2807106; 2901259</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2663191; 2759808</t>
+          <t>2663723; 2756120</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2713392; 2798214</t>
+          <t>2712791; 2798060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3070752; 3152914</t>
+          <t>3078052; 3157898</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2906414; 2999309</t>
+          <t>2902820; 2994356</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5185270; 5322071</t>
+          <t>5188156; 5314879</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5907117; 6026951</t>
+          <t>5907769; 6028474</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5597182; 5726172</t>
+          <t>5591746; 5728970</t>
         </is>
       </c>
     </row>
